--- a/工場の質問箱_質問登録.xlsx
+++ b/工場の質問箱_質問登録.xlsx
@@ -736,19 +736,47 @@
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="3">
-        <f>ROW()-1</f>
-        <v/>
-      </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>よくある質問</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>作業工程</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>ドリルの芯振れはどう確認しますか</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>芯振れ,ドリルの芯,振れ,芯の確認</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>ドリルの芯振れの確認手順です。
+1. 操作盤を確認する
+2. M68を入力してミーリングモードにし、主軸を固定する
+3. ピックを主軸に取り付けてドリルに当てる
+4. 扉を閉めて芯を確認する。振れは0.02以下
+動画: shinbure</t>
+        </is>
+      </c>
       <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n"/>
-      <c r="J2" s="6" t="n"/>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="7">
